--- a/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42D3B2DE-D33B-45DA-9B98-22C84DBCECB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6809E06-8695-4B9A-BF3D-113F6A575117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -307,105 +307,9 @@
     <t>IND</t>
   </si>
   <si>
-    <t>w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>IN684-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - IN684-765_IND</t>
-  </si>
-  <si>
-    <t>w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w331275940-765_IND</t>
-  </si>
-  <si>
     <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
   </si>
   <si>
-    <t>w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>at grid node - w203673991-400_IND</t>
-  </si>
-  <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
@@ -424,7 +328,103 @@
     <t>ELE,CHP</t>
   </si>
   <si>
+    <t>Vadodara_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Vadodara_IND</t>
+  </si>
+  <si>
     <t>en_gas_ccgt,en_gas_turbine,en_chp_gas_cc_ext,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_nuclear,en_nuclear_smr,en_biomass,en_chp_biomass_chips_ext,en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw,en_chp_gas_cc_ext_ccs</t>
+  </si>
+  <si>
+    <t>Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>Jaipur_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Jaipur_IND</t>
+  </si>
+  <si>
+    <t>Wardha_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Wardha_IND</t>
+  </si>
+  <si>
+    <t>Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>Solapur_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Solapur_IND</t>
+  </si>
+  <si>
+    <t>Korba_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Korba_IND</t>
+  </si>
+  <si>
+    <t>Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>Medinipur_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Medinipur_IND</t>
+  </si>
+  <si>
+    <t>Kurnool_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Kurnool_IND</t>
+  </si>
+  <si>
+    <t>Bhuj_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Bhuj_IND</t>
+  </si>
+  <si>
+    <t>Indore_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Indore_IND</t>
+  </si>
+  <si>
+    <t>Moga_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Moga_IND</t>
+  </si>
+  <si>
+    <t>Phalodi_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Phalodi_IND</t>
+  </si>
+  <si>
+    <t>Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>Tezpur_IND</t>
+  </si>
+  <si>
+    <t>at grid node - Tezpur_IND</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -848,46 +848,46 @@
         <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G11" t="s">
         <v>88</v>
       </c>
       <c r="H11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J11" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="L11" t="s">
         <v>88</v>
       </c>
       <c r="M11" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="N11" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="O11" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="Q11" t="s">
         <v>88</v>
       </c>
       <c r="R11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="S11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="T11" t="s">
         <v>129</v>
@@ -898,46 +898,46 @@
         <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G12" t="s">
         <v>88</v>
       </c>
       <c r="H12" t="s">
+        <v>107</v>
+      </c>
+      <c r="I12" t="s">
+        <v>108</v>
+      </c>
+      <c r="J12" t="s">
+        <v>89</v>
+      </c>
+      <c r="L12" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N12" t="s">
+        <v>126</v>
+      </c>
+      <c r="O12" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>88</v>
+      </c>
+      <c r="R12" t="s">
         <v>105</v>
       </c>
-      <c r="I12" t="s">
+      <c r="S12" t="s">
         <v>106</v>
-      </c>
-      <c r="J12" t="s">
-        <v>119</v>
-      </c>
-      <c r="L12" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" t="s">
-        <v>113</v>
-      </c>
-      <c r="N12" t="s">
-        <v>114</v>
-      </c>
-      <c r="O12" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>88</v>
-      </c>
-      <c r="R12" t="s">
-        <v>101</v>
-      </c>
-      <c r="S12" t="s">
-        <v>102</v>
       </c>
       <c r="T12" t="s">
         <v>129</v>
@@ -948,46 +948,46 @@
         <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G13" t="s">
         <v>88</v>
       </c>
       <c r="H13" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="I13" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="J13" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="L13" t="s">
         <v>88</v>
       </c>
       <c r="M13" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="N13" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="O13" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="Q13" t="s">
         <v>88</v>
       </c>
       <c r="R13" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="S13" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="T13" t="s">
         <v>129</v>
@@ -998,46 +998,46 @@
         <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" t="s">
         <v>98</v>
       </c>
-      <c r="E14" t="s">
-        <v>128</v>
-      </c>
       <c r="G14" t="s">
         <v>88</v>
       </c>
       <c r="H14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="I14" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J14" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="L14" t="s">
         <v>88</v>
       </c>
       <c r="M14" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="N14" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="Q14" t="s">
         <v>88</v>
       </c>
       <c r="R14" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="S14" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="T14" t="s">
         <v>129</v>
@@ -1048,46 +1048,46 @@
         <v>88</v>
       </c>
       <c r="C15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" t="s">
         <v>101</v>
       </c>
-      <c r="D15" t="s">
+      <c r="I15" t="s">
         <v>102</v>
       </c>
-      <c r="E15" t="s">
-        <v>128</v>
-      </c>
-      <c r="G15" t="s">
-        <v>88</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
+        <v>89</v>
+      </c>
+      <c r="L15" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" t="s">
+        <v>115</v>
+      </c>
+      <c r="N15" t="s">
+        <v>116</v>
+      </c>
+      <c r="O15" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>88</v>
+      </c>
+      <c r="R15" t="s">
         <v>99</v>
       </c>
-      <c r="I15" t="s">
+      <c r="S15" t="s">
         <v>100</v>
-      </c>
-      <c r="J15" t="s">
-        <v>119</v>
-      </c>
-      <c r="L15" t="s">
-        <v>88</v>
-      </c>
-      <c r="M15" t="s">
-        <v>93</v>
-      </c>
-      <c r="N15" t="s">
-        <v>94</v>
-      </c>
-      <c r="O15" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>88</v>
-      </c>
-      <c r="R15" t="s">
-        <v>93</v>
-      </c>
-      <c r="S15" t="s">
-        <v>94</v>
       </c>
       <c r="T15" t="s">
         <v>129</v>
@@ -1098,46 +1098,46 @@
         <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G16" t="s">
         <v>88</v>
       </c>
       <c r="H16" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" t="s">
+        <v>104</v>
+      </c>
+      <c r="J16" t="s">
+        <v>89</v>
+      </c>
+      <c r="L16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" t="s">
+        <v>113</v>
+      </c>
+      <c r="N16" t="s">
+        <v>114</v>
+      </c>
+      <c r="O16" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>88</v>
+      </c>
+      <c r="R16" t="s">
+        <v>96</v>
+      </c>
+      <c r="S16" t="s">
         <v>97</v>
-      </c>
-      <c r="I16" t="s">
-        <v>98</v>
-      </c>
-      <c r="J16" t="s">
-        <v>119</v>
-      </c>
-      <c r="L16" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16" t="s">
-        <v>117</v>
-      </c>
-      <c r="N16" t="s">
-        <v>118</v>
-      </c>
-      <c r="O16" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>88</v>
-      </c>
-      <c r="R16" t="s">
-        <v>117</v>
-      </c>
-      <c r="S16" t="s">
-        <v>118</v>
       </c>
       <c r="T16" t="s">
         <v>129</v>
@@ -1148,46 +1148,46 @@
         <v>88</v>
       </c>
       <c r="C17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" t="s">
+        <v>109</v>
+      </c>
+      <c r="I17" t="s">
+        <v>110</v>
+      </c>
+      <c r="J17" t="s">
         <v>89</v>
       </c>
-      <c r="D17" t="s">
+      <c r="L17" t="s">
+        <v>88</v>
+      </c>
+      <c r="M17" t="s">
+        <v>117</v>
+      </c>
+      <c r="N17" t="s">
+        <v>118</v>
+      </c>
+      <c r="O17" t="s">
         <v>90</v>
       </c>
-      <c r="E17" t="s">
+      <c r="Q17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R17" t="s">
+        <v>127</v>
+      </c>
+      <c r="S17" t="s">
         <v>128</v>
-      </c>
-      <c r="G17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" t="s">
-        <v>90</v>
-      </c>
-      <c r="J17" t="s">
-        <v>119</v>
-      </c>
-      <c r="L17" t="s">
-        <v>88</v>
-      </c>
-      <c r="M17" t="s">
-        <v>99</v>
-      </c>
-      <c r="N17" t="s">
-        <v>100</v>
-      </c>
-      <c r="O17" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>88</v>
-      </c>
-      <c r="R17" t="s">
-        <v>120</v>
-      </c>
-      <c r="S17" t="s">
-        <v>121</v>
       </c>
       <c r="T17" t="s">
         <v>129</v>
@@ -1198,46 +1198,46 @@
         <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G18" t="s">
         <v>88</v>
       </c>
       <c r="H18" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="I18" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="J18" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="L18" t="s">
         <v>88</v>
       </c>
       <c r="M18" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="N18" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="O18" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="Q18" t="s">
         <v>88</v>
       </c>
       <c r="R18" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="S18" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="T18" t="s">
         <v>129</v>
@@ -1248,46 +1248,46 @@
         <v>88</v>
       </c>
       <c r="C19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" t="s">
+        <v>123</v>
+      </c>
+      <c r="I19" t="s">
+        <v>124</v>
+      </c>
+      <c r="J19" t="s">
+        <v>89</v>
+      </c>
+      <c r="L19" t="s">
+        <v>88</v>
+      </c>
+      <c r="M19" t="s">
         <v>107</v>
       </c>
-      <c r="D19" t="s">
+      <c r="N19" t="s">
         <v>108</v>
       </c>
-      <c r="E19" t="s">
-        <v>128</v>
-      </c>
-      <c r="G19" t="s">
-        <v>88</v>
-      </c>
-      <c r="H19" t="s">
-        <v>113</v>
-      </c>
-      <c r="I19" t="s">
-        <v>114</v>
-      </c>
-      <c r="J19" t="s">
-        <v>119</v>
-      </c>
-      <c r="L19" t="s">
-        <v>88</v>
-      </c>
-      <c r="M19" t="s">
-        <v>89</v>
-      </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>90</v>
       </c>
-      <c r="O19" t="s">
-        <v>122</v>
-      </c>
       <c r="Q19" t="s">
         <v>88</v>
       </c>
       <c r="R19" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="S19" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="T19" t="s">
         <v>129</v>
@@ -1298,25 +1298,25 @@
         <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="E20" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G20" t="s">
         <v>88</v>
       </c>
       <c r="H20" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="I20" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="J20" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="L20" t="s">
         <v>88</v>
@@ -1328,16 +1328,16 @@
         <v>102</v>
       </c>
       <c r="O20" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="Q20" t="s">
         <v>88</v>
       </c>
       <c r="R20" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="S20" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="T20" t="s">
         <v>129</v>
@@ -1348,46 +1348,46 @@
         <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" t="s">
+        <v>127</v>
+      </c>
+      <c r="I21" t="s">
         <v>128</v>
       </c>
-      <c r="G21" t="s">
-        <v>88</v>
-      </c>
-      <c r="H21" t="s">
-        <v>120</v>
-      </c>
-      <c r="I21" t="s">
-        <v>121</v>
-      </c>
       <c r="J21" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="L21" t="s">
         <v>88</v>
       </c>
       <c r="M21" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="N21" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="O21" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="Q21" t="s">
         <v>88</v>
       </c>
       <c r="R21" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="S21" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="T21" t="s">
         <v>129</v>
@@ -1398,46 +1398,46 @@
         <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G22" t="s">
         <v>88</v>
       </c>
       <c r="H22" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="I22" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="J22" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="L22" t="s">
         <v>88</v>
       </c>
       <c r="M22" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="N22" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="O22" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="Q22" t="s">
         <v>88</v>
       </c>
       <c r="R22" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="S22" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="T22" t="s">
         <v>129</v>
@@ -1448,46 +1448,46 @@
         <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E23" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" t="s">
+        <v>117</v>
+      </c>
+      <c r="I23" t="s">
+        <v>118</v>
+      </c>
+      <c r="J23" t="s">
+        <v>89</v>
+      </c>
+      <c r="L23" t="s">
+        <v>88</v>
+      </c>
+      <c r="M23" t="s">
+        <v>127</v>
+      </c>
+      <c r="N23" t="s">
         <v>128</v>
       </c>
-      <c r="G23" t="s">
-        <v>88</v>
-      </c>
-      <c r="H23" t="s">
-        <v>109</v>
-      </c>
-      <c r="I23" t="s">
-        <v>110</v>
-      </c>
-      <c r="J23" t="s">
-        <v>119</v>
-      </c>
-      <c r="L23" t="s">
-        <v>88</v>
-      </c>
-      <c r="M23" t="s">
-        <v>115</v>
-      </c>
-      <c r="N23" t="s">
-        <v>116</v>
-      </c>
       <c r="O23" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="Q23" t="s">
         <v>88</v>
       </c>
       <c r="R23" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T23" t="s">
         <v>129</v>
@@ -1498,37 +1498,37 @@
         <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G24" t="s">
         <v>88</v>
       </c>
       <c r="H24" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I24" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J24" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="L24" t="s">
         <v>88</v>
       </c>
       <c r="M24" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="N24" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="O24" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.25">
@@ -1536,37 +1536,37 @@
         <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G25" t="s">
         <v>88</v>
       </c>
       <c r="H25" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="I25" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="J25" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="L25" t="s">
         <v>88</v>
       </c>
       <c r="M25" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="O25" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
@@ -1574,25 +1574,25 @@
         <v>88</v>
       </c>
       <c r="H26" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="I26" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="J26" t="s">
+        <v>89</v>
+      </c>
+      <c r="L26" t="s">
+        <v>88</v>
+      </c>
+      <c r="M26" t="s">
         <v>119</v>
       </c>
-      <c r="L26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M26" t="s">
-        <v>95</v>
-      </c>
       <c r="N26" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="O26" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="D29" t="s">
         <v>6</v>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="3:24" x14ac:dyDescent="0.25">
@@ -3003,7 +3003,7 @@
         <v>66</v>
       </c>
       <c r="F49" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="G49" t="s">
         <v>65</v>
@@ -3020,7 +3020,7 @@
         <v>67</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="G50" t="s">
         <v>68</v>
@@ -3048,7 +3048,7 @@
         <v>2100</v>
       </c>
       <c r="F52" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.25">

--- a/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEA15BE-65B0-400C-B32F-4C32BFBD8447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AD9424-4F78-4FB6-9DA9-544AE705E588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -845,10 +845,10 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O11" t="s">
         <v>113</v>
@@ -907,10 +907,10 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="N12" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="O12" t="s">
         <v>113</v>
@@ -969,10 +969,10 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="N13" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="O13" t="s">
         <v>113</v>
@@ -1031,10 +1031,10 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O14" t="s">
         <v>113</v>
@@ -1093,10 +1093,10 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="N15" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O15" t="s">
         <v>113</v>
@@ -1279,10 +1279,10 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="N18" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="O18" t="s">
         <v>113</v>
@@ -1341,10 +1341,10 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="N19" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="O19" t="s">
         <v>113</v>
@@ -1403,10 +1403,10 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="N20" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="O20" t="s">
         <v>113</v>
@@ -1465,10 +1465,10 @@
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="N21" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="O21" t="s">
         <v>113</v>
@@ -1589,10 +1589,10 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="N23" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="O23" t="s">
         <v>113</v>
@@ -1651,10 +1651,10 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="N24" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="O24" t="s">
         <v>113</v>
@@ -1689,10 +1689,10 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="N25" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="O25" t="s">
         <v>113</v>

--- a/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AD9424-4F78-4FB6-9DA9-544AE705E588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEE9B1E-5292-4DC6-9075-5007A03F0B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="116">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -845,10 +845,10 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="O11" t="s">
         <v>113</v>
@@ -907,10 +907,10 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="N12" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="O12" t="s">
         <v>113</v>
@@ -969,10 +969,10 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="N13" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="O13" t="s">
         <v>113</v>
@@ -1031,10 +1031,10 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="N14" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="O14" t="s">
         <v>113</v>
@@ -1093,10 +1093,10 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="N15" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O15" t="s">
         <v>113</v>
@@ -1155,10 +1155,10 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="N16" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="O16" t="s">
         <v>113</v>
@@ -1167,10 +1167,10 @@
         <v>78</v>
       </c>
       <c r="R16" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="S16" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="T16" t="s">
         <v>114</v>
@@ -1179,10 +1179,10 @@
         <v>78</v>
       </c>
       <c r="W16" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="X16" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="Y16" t="s">
         <v>115</v>
@@ -1217,10 +1217,10 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="N17" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="O17" t="s">
         <v>113</v>
@@ -1229,10 +1229,10 @@
         <v>78</v>
       </c>
       <c r="R17" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="S17" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="T17" t="s">
         <v>114</v>
@@ -1241,10 +1241,10 @@
         <v>78</v>
       </c>
       <c r="W17" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="X17" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="Y17" t="s">
         <v>115</v>
@@ -1279,10 +1279,10 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="N18" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="O18" t="s">
         <v>113</v>
@@ -1291,10 +1291,10 @@
         <v>78</v>
       </c>
       <c r="R18" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="S18" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="T18" t="s">
         <v>114</v>
@@ -1303,10 +1303,10 @@
         <v>78</v>
       </c>
       <c r="W18" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="X18" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="Y18" t="s">
         <v>115</v>
@@ -1341,10 +1341,10 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="N19" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="O19" t="s">
         <v>113</v>
@@ -1353,10 +1353,10 @@
         <v>78</v>
       </c>
       <c r="R19" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="S19" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="T19" t="s">
         <v>114</v>
@@ -1365,10 +1365,10 @@
         <v>78</v>
       </c>
       <c r="W19" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="X19" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="Y19" t="s">
         <v>115</v>
@@ -1403,10 +1403,10 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="N20" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="O20" t="s">
         <v>113</v>
@@ -1415,10 +1415,10 @@
         <v>78</v>
       </c>
       <c r="R20" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="S20" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="T20" t="s">
         <v>114</v>
@@ -1427,10 +1427,10 @@
         <v>78</v>
       </c>
       <c r="W20" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="X20" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="Y20" t="s">
         <v>115</v>
@@ -1465,10 +1465,10 @@
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="N21" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="O21" t="s">
         <v>113</v>
@@ -1477,10 +1477,10 @@
         <v>78</v>
       </c>
       <c r="R21" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="S21" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="T21" t="s">
         <v>114</v>
@@ -1489,10 +1489,10 @@
         <v>78</v>
       </c>
       <c r="W21" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="X21" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="Y21" t="s">
         <v>115</v>
@@ -1539,10 +1539,10 @@
         <v>78</v>
       </c>
       <c r="R22" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="S22" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="T22" t="s">
         <v>114</v>
@@ -1551,10 +1551,10 @@
         <v>78</v>
       </c>
       <c r="W22" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="X22" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="Y22" t="s">
         <v>115</v>
@@ -1589,10 +1589,10 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="N23" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="O23" t="s">
         <v>113</v>
@@ -1601,10 +1601,10 @@
         <v>78</v>
       </c>
       <c r="R23" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="S23" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="T23" t="s">
         <v>114</v>
@@ -1613,10 +1613,10 @@
         <v>78</v>
       </c>
       <c r="W23" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="X23" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="Y23" t="s">
         <v>115</v>
@@ -1651,14 +1651,38 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="N24" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="O24" t="s">
         <v>113</v>
       </c>
+      <c r="Q24" t="s">
+        <v>78</v>
+      </c>
+      <c r="R24" t="s">
+        <v>84</v>
+      </c>
+      <c r="S24" t="s">
+        <v>85</v>
+      </c>
+      <c r="T24" t="s">
+        <v>114</v>
+      </c>
+      <c r="V24" t="s">
+        <v>78</v>
+      </c>
+      <c r="W24" t="s">
+        <v>84</v>
+      </c>
+      <c r="X24" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
@@ -1689,10 +1713,10 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="N25" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="O25" t="s">
         <v>113</v>
@@ -1715,10 +1739,10 @@
         <v>78</v>
       </c>
       <c r="M26" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="N26" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="O26" t="s">
         <v>113</v>
